--- a/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>AS</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,149 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1182900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1315000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1146300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>856800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1050300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1198700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>847400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>693500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>809200</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>544400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>631800</v>
+      </c>
+      <c r="F9" s="3">
         <v>564900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>400200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>495400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>596700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>415200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>364700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>408600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>638500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>683200</v>
+      </c>
+      <c r="F10" s="3">
         <v>581400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>456600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>554900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>602000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>432200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>328800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>400600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +835,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,8 +866,14 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,37 +901,49 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F14" s="3">
         <v>-2900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>4700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>2800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>200800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-2700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>2800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,8 +971,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,66 +987,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1094200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1263000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1043300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>850200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>920600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1266000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>776600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>706700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>760200</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>52000</v>
+      </c>
+      <c r="F18" s="3">
         <v>103000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>6600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>129700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-67300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>70800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-13200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>49000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,153 +1072,185 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-73600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>3500</v>
       </c>
       <c r="H20" s="3">
         <v>-500</v>
       </c>
       <c r="I20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>3600</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>105500</v>
+      </c>
+      <c r="F21" s="3">
         <v>157800</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <v>218000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>88900</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>98200</v>
+      </c>
+      <c r="F22" s="3">
         <v>107000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>97600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>83600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>61100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>55000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>54200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>60100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-55100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-91800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>45600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-124900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>15300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-65400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>39800</v>
+      </c>
+      <c r="F24" s="3">
         <v>32600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>5200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>26600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>23400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>17000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>11700</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,66 +1278,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-35900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-97000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>19000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-148300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-61600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-19200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-35900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-97000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>19000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-148300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-61600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-19200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,37 +1383,49 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-11500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-9800</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,66 +1488,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-3500</v>
       </c>
       <c r="H32" s="3">
         <v>500</v>
       </c>
       <c r="I32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-3600</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-35900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-97000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>19000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-148300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-73100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-29000</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,71 +1593,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-35900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-97000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>19000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-148300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-73100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-29000</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,23 +1702,25 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>337300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>483400</v>
+      </c>
+      <c r="F41" s="3">
         <v>284200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>278500</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1560,8 +1733,14 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1589,23 +1768,29 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>567100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>606400</v>
+      </c>
+      <c r="F43" s="3">
         <v>676900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>436300</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,23 +1803,29 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1100600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1099600</v>
+      </c>
+      <c r="F44" s="3">
         <v>1197500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1219200</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1647,23 +1838,29 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>164700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>162300</v>
+      </c>
+      <c r="F45" s="3">
         <v>201500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>206400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,23 +1873,29 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2169700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2351700</v>
+      </c>
+      <c r="F46" s="3">
         <v>2360100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2140400</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1705,23 +1908,29 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F47" s="3">
         <v>8800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>8600</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,23 +1943,29 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>799000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>759000</v>
+      </c>
+      <c r="F48" s="3">
         <v>651100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>579500</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1763,23 +1978,29 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4966800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5018700</v>
+      </c>
+      <c r="F49" s="3">
         <v>4948200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5007600</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1792,8 +2013,14 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,23 +2083,29 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>229900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>235200</v>
+      </c>
+      <c r="F52" s="3">
         <v>178800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>178100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1879,8 +2118,14 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,23 +2153,29 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8174500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8373800</v>
+      </c>
+      <c r="F54" s="3">
         <v>8147000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7914200</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1937,8 +2188,14 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,23 +2222,25 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>387400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>426500</v>
+      </c>
+      <c r="F57" s="3">
         <v>389400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>434200</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
@@ -1992,23 +2253,29 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>99900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>470400</v>
+      </c>
+      <c r="F58" s="3">
         <v>456300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>335000</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2021,23 +2288,29 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>618900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>677000</v>
+      </c>
+      <c r="F59" s="3">
         <v>589300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>442000</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2050,23 +2323,29 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1106200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1573900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1435000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1211200</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2079,23 +2358,29 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2301000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6190800</v>
+      </c>
+      <c r="F61" s="3">
         <v>5982700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6091900</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2108,23 +2393,29 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>741600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>765900</v>
+      </c>
+      <c r="F62" s="3">
         <v>720500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>725100</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2137,8 +2428,14 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,23 +2533,29 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4154000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8534000</v>
+      </c>
+      <c r="F66" s="3">
         <v>8143500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8031700</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2253,8 +2568,14 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2688,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,23 +2723,29 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1863600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-833000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-811000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-830400</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2411,8 +2758,14 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,23 +2863,29 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4020500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-160200</v>
+      </c>
+      <c r="F76" s="3">
         <v>3500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-117500</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,8 +2898,14 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,71 +2933,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-35900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-97000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>19000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-148300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-73100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-29000</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,37 +3027,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>62400</v>
+      </c>
+      <c r="F83" s="3">
         <v>54100</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>147700</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>116500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>305100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-39200</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-179700</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,26 +3287,28 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-55700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-37400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-58700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-36400</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -2877,8 +3318,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3388,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-39300</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-82400</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3442,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3473,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,91 +3578,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-184900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-62300</v>
+      </c>
+      <c r="F100" s="3">
         <v>92600</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>47800</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-8400</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-73700</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-146100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>199100</v>
+      </c>
+      <c r="F102" s="3">
         <v>5700</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3">
         <v>-288000</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>AS</t>
   </si>
@@ -656,174 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>993800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1182900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1315000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1146300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>856800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1050300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1198700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>847400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>693500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>809200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>442500</v>
+      </c>
+      <c r="E9" s="3">
         <v>544400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>631800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>564900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>400200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>495400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>596700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>415200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>364700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>408600</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>551300</v>
+      </c>
+      <c r="E10" s="3">
         <v>638500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>683200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>581400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>456600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>554900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>602000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>432200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>328800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>400600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +850,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +886,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,43 +924,49 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
         <v>15600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1015,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1003900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1094200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1263000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1043300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>850200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>920600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1266000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>776600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>706700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>760200</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E18" s="3">
         <v>88700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>52000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>103000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>129700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-67300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>70800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>49000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,183 +1107,199 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-73600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3600</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E21" s="3">
         <v>77600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>105500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>157800</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>218000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>88900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>98200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>107000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>97600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>83600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>61100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>55000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>54200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>60100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="E23" s="3">
         <v>15100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-55100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-91800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>45600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-124900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-65400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-51900</v>
+      </c>
+      <c r="E24" s="3">
         <v>8200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>32600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>23400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11700</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1333,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>6900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-94900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-35900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-97000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-148300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-61600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>5100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-94700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-97000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-148300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-61600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19200</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,19 +1447,22 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>3</v>
@@ -1409,23 +1470,26 @@
       <c r="H29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-11500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-9800</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1561,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E32" s="3">
         <v>73600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3600</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>5100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-94700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-97000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-148300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-73100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1675,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>5100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-94700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-97000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-148300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-73100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,26 +1790,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E41" s="3">
         <v>337300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>483400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>284200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>278500</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1739,8 +1826,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1774,26 +1864,29 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>476600</v>
+      </c>
+      <c r="E43" s="3">
         <v>567100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>606400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>676900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>436300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,26 +1902,29 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1241000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1100600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1099600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1197500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1219200</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1844,26 +1940,29 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>219200</v>
+      </c>
+      <c r="E45" s="3">
         <v>164700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>162300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>201500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>206400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1879,26 +1978,29 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2192700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2169700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2351700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2360100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2140400</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1914,26 +2016,29 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E47" s="3">
         <v>9100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8600</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1949,26 +2054,29 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>883900</v>
+      </c>
+      <c r="E48" s="3">
         <v>799000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>759000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>651100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>579500</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1984,26 +2092,29 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4946800</v>
+      </c>
+      <c r="E49" s="3">
         <v>4966800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5018700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4948200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5007600</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,8 +2130,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,26 +2206,29 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>212300</v>
+      </c>
+      <c r="E52" s="3">
         <v>229900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>235200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>178800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>178100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2124,8 +2244,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,26 +2282,29 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8244700</v>
+      </c>
+      <c r="E54" s="3">
         <v>8174500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8373800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8147000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7914200</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2194,8 +2320,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,26 +2354,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>454300</v>
+      </c>
+      <c r="E57" s="3">
         <v>387400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>426500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>389400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>434200</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2259,26 +2390,29 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E58" s="3">
         <v>99900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>470400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>456300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>335000</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2294,26 +2428,29 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>583200</v>
+      </c>
+      <c r="E59" s="3">
         <v>618900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>677000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>589300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>442000</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,26 +2466,29 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1170800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1106200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1573900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1435000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1211200</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,26 +2504,29 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2343700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2301000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6190800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5982700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6091900</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2399,26 +2542,29 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>716500</v>
+      </c>
+      <c r="E62" s="3">
         <v>741600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>765900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>720500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>725100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2580,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,26 +2694,29 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4238100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4154000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8534000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8143500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8031700</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2574,8 +2732,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,26 +2900,29 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1847900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1863600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-833000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-811000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-830400</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2764,8 +2938,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,26 +3052,29 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4006600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4020500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-160200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-117500</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,8 +3090,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3128,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>5100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-94700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-97000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-148300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-73100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3227,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E83" s="3">
         <v>62500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>62400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>54100</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>147700</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E89" s="3">
         <v>116500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>305100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-39200</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-179700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,29 +3509,30 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-67300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36400</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -3324,8 +3545,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3621,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-67300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-59200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-39300</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-82400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3677,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3713,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +3827,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-184900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-62300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>92600</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>47800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8400</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-73700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-81400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-146100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>199100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5700</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K102" s="3">
         <v>-288000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>AS</t>
   </si>
@@ -656,187 +656,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>993800</v>
+        <v>1353800</v>
       </c>
       <c r="E8" s="3">
+        <v>1011100</v>
+      </c>
+      <c r="F8" s="3">
         <v>1182900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1315000</v>
       </c>
-      <c r="G8" s="3">
-        <v>1146300</v>
-      </c>
       <c r="H8" s="3">
-        <v>856800</v>
+        <v>1153100</v>
       </c>
       <c r="I8" s="3">
+        <v>869500</v>
+      </c>
+      <c r="J8" s="3">
         <v>1050300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1198700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>847400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>693500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>809200</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>442500</v>
+        <v>606500</v>
       </c>
       <c r="E9" s="3">
+        <v>442600</v>
+      </c>
+      <c r="F9" s="3">
         <v>544400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>631800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>564900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>400200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>495400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>596700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>415200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>364700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>408600</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>551300</v>
+        <v>747300</v>
       </c>
       <c r="E10" s="3">
+        <v>568500</v>
+      </c>
+      <c r="F10" s="3">
         <v>638500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>683200</v>
       </c>
-      <c r="G10" s="3">
-        <v>581400</v>
-      </c>
       <c r="H10" s="3">
-        <v>456600</v>
+        <v>588200</v>
       </c>
       <c r="I10" s="3">
+        <v>469300</v>
+      </c>
+      <c r="J10" s="3">
         <v>554900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>602000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>432200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>328800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400600</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +864,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +903,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,69 +944,75 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15600</v>
       </c>
-      <c r="F14" s="3">
-        <v>-2200</v>
-      </c>
       <c r="G14" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="H14" s="3">
         <v>-2900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>38900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>33400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>32800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>33100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>33200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1003,8 +1026,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1042,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1003900</v>
+        <v>1177100</v>
       </c>
       <c r="E17" s="3">
-        <v>1094200</v>
+        <v>1018400</v>
       </c>
       <c r="F17" s="3">
-        <v>1263000</v>
+        <v>1072600</v>
       </c>
       <c r="G17" s="3">
-        <v>1043300</v>
+        <v>1257900</v>
       </c>
       <c r="H17" s="3">
-        <v>850200</v>
+        <v>1051300</v>
       </c>
       <c r="I17" s="3">
-        <v>920600</v>
+        <v>857300</v>
       </c>
       <c r="J17" s="3">
+        <v>917100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1266000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>776600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>706700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>760200</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-10100</v>
+        <v>176700</v>
       </c>
       <c r="E18" s="3">
-        <v>88700</v>
+        <v>-7300</v>
       </c>
       <c r="F18" s="3">
-        <v>52000</v>
+        <v>110300</v>
       </c>
       <c r="G18" s="3">
-        <v>103000</v>
+        <v>57100</v>
       </c>
       <c r="H18" s="3">
-        <v>6600</v>
+        <v>101800</v>
       </c>
       <c r="I18" s="3">
-        <v>129700</v>
+        <v>12200</v>
       </c>
       <c r="J18" s="3">
+        <v>133200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-67300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>70800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>49000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,198 +1141,214 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-43600</v>
+        <v>4800</v>
       </c>
       <c r="E20" s="3">
-        <v>-73600</v>
+        <v>5200</v>
       </c>
       <c r="F20" s="3">
-        <v>-8900</v>
+        <v>14000</v>
       </c>
       <c r="G20" s="3">
-        <v>700</v>
+        <v>7400</v>
       </c>
       <c r="H20" s="3">
-        <v>-800</v>
+        <v>2400</v>
       </c>
       <c r="I20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3600</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>9100</v>
+        <v>210800</v>
       </c>
       <c r="E21" s="3">
-        <v>77600</v>
+        <v>21100</v>
       </c>
       <c r="F21" s="3">
-        <v>105500</v>
+        <v>132300</v>
       </c>
       <c r="G21" s="3">
-        <v>157800</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
+        <v>83100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>132200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>41800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>163900</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>218000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>88900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>42500</v>
       </c>
       <c r="F22" s="3">
-        <v>98200</v>
+        <v>68300</v>
       </c>
       <c r="G22" s="3">
+        <v>109400</v>
+      </c>
+      <c r="H22" s="3">
         <v>107000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>97600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>83600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>61100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>55000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>54200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>60100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>128900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-53700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-55100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-91800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>45600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-124900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-65400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7500</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-51900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>32600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>23400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11700</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1385,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-94900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-97000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-148300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-61600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19200</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-94700</v>
-      </c>
       <c r="G27" s="3">
-        <v>-35900</v>
+        <v>-93000</v>
       </c>
       <c r="H27" s="3">
-        <v>-97000</v>
+        <v>-37700</v>
       </c>
       <c r="I27" s="3">
+        <v>-96900</v>
+      </c>
+      <c r="J27" s="3">
         <v>19000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-148300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-61600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19200</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,46 +1508,52 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-11500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-9800</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1631,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>43600</v>
+        <v>-4800</v>
       </c>
       <c r="E32" s="3">
-        <v>73600</v>
+        <v>-5200</v>
       </c>
       <c r="F32" s="3">
-        <v>8900</v>
+        <v>-14000</v>
       </c>
       <c r="G32" s="3">
-        <v>-700</v>
+        <v>-7400</v>
       </c>
       <c r="H32" s="3">
-        <v>800</v>
+        <v>-2400</v>
       </c>
       <c r="I32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>500</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3600</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-94700</v>
-      </c>
       <c r="G33" s="3">
-        <v>-35900</v>
+        <v>-93000</v>
       </c>
       <c r="H33" s="3">
-        <v>-97000</v>
+        <v>-37700</v>
       </c>
       <c r="I33" s="3">
+        <v>-96900</v>
+      </c>
+      <c r="J33" s="3">
         <v>19000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-148300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-73100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-29000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1754,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-94700</v>
-      </c>
       <c r="G35" s="3">
-        <v>-35900</v>
+        <v>-93000</v>
       </c>
       <c r="H35" s="3">
-        <v>-97000</v>
+        <v>-37700</v>
       </c>
       <c r="I35" s="3">
+        <v>-96900</v>
+      </c>
+      <c r="J35" s="3">
         <v>19000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-148300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-73100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-29000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,29 +1877,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>312000</v>
+      </c>
+      <c r="E41" s="3">
         <v>255900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>337300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>483400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>284200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>278500</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1829,8 +1916,11 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,28 +1957,31 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>881900</v>
+      </c>
+      <c r="E43" s="3">
         <v>476600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>567100</v>
       </c>
-      <c r="F43" s="3">
-        <v>606400</v>
-      </c>
       <c r="G43" s="3">
+        <v>716500</v>
+      </c>
+      <c r="H43" s="3">
         <v>676900</v>
       </c>
-      <c r="H43" s="3">
-        <v>436300</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3">
+        <v>469400</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1905,29 +1998,32 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1338500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1241000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1100600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1099600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1197500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1219200</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,28 +2039,31 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>219200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>164700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>162300</v>
+        <v>15900</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>201500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>206400</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+        <v>13000</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
+        <v>26200</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1981,29 +2080,32 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2548300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2192700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2169700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2351700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2360100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2140400</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,8 +2121,11 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2028,20 +2133,20 @@
         <v>9000</v>
       </c>
       <c r="E47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F47" s="3">
         <v>9100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8600</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2057,28 +2162,31 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>883900</v>
+        <v>950400</v>
       </c>
       <c r="E48" s="3">
-        <v>799000</v>
+        <v>806900</v>
       </c>
       <c r="F48" s="3">
-        <v>759000</v>
+        <v>713100</v>
       </c>
       <c r="G48" s="3">
-        <v>651100</v>
+        <v>684100</v>
       </c>
       <c r="H48" s="3">
-        <v>579500</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
+        <v>605200</v>
+      </c>
+      <c r="I48" s="3">
+        <v>526200</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -2095,31 +2203,34 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5029100</v>
+      </c>
+      <c r="E49" s="3">
         <v>4946800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4966800</v>
       </c>
-      <c r="F49" s="3">
-        <v>5018700</v>
-      </c>
       <c r="G49" s="3">
+        <v>5014600</v>
+      </c>
+      <c r="H49" s="3">
         <v>4948200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5007600</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2133,8 +2244,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,28 +2326,31 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>212300</v>
+        <v>121900</v>
       </c>
       <c r="E52" s="3">
-        <v>229900</v>
+        <v>133700</v>
       </c>
       <c r="F52" s="3">
-        <v>235200</v>
+        <v>155500</v>
       </c>
       <c r="G52" s="3">
-        <v>178800</v>
+        <v>152500</v>
       </c>
       <c r="H52" s="3">
-        <v>178100</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+        <v>115100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>120600</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2247,8 +2367,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,29 +2408,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8828400</v>
+      </c>
+      <c r="E54" s="3">
         <v>8244700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8174500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8373800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8147000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7914200</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2323,8 +2449,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,29 +2485,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>482300</v>
+      </c>
+      <c r="E57" s="3">
         <v>454300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>387400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>426500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>389400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>434200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,31 +2524,34 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>394900</v>
+      </c>
+      <c r="E58" s="3">
         <v>133300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>99900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>470400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>456300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>335000</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2431,29 +2565,32 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>583200</v>
+        <v>199100</v>
       </c>
       <c r="E59" s="3">
-        <v>618900</v>
+        <v>126600</v>
       </c>
       <c r="F59" s="3">
-        <v>677000</v>
+        <v>193800</v>
       </c>
       <c r="G59" s="3">
+        <v>226900</v>
+      </c>
+      <c r="H59" s="3">
         <v>589300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>442000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,29 +2606,32 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1571400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1170800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1106200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1573900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1435000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1211200</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2507,29 +2647,32 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2392500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2343700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2301000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6190800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5982700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6091900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2545,28 +2688,31 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>716500</v>
+        <v>66200</v>
       </c>
       <c r="E62" s="3">
-        <v>741600</v>
+        <v>39800</v>
       </c>
       <c r="F62" s="3">
-        <v>765900</v>
+        <v>57700</v>
       </c>
       <c r="G62" s="3">
-        <v>720500</v>
+        <v>67000</v>
       </c>
       <c r="H62" s="3">
-        <v>725100</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+        <v>48700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>46000</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2583,8 +2729,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,28 +2852,31 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4238100</v>
+        <v>4716100</v>
       </c>
       <c r="E66" s="3">
-        <v>4154000</v>
+        <v>4231000</v>
       </c>
       <c r="F66" s="3">
-        <v>8534000</v>
+        <v>4148800</v>
       </c>
       <c r="G66" s="3">
-        <v>8143500</v>
+        <v>8530600</v>
       </c>
       <c r="H66" s="3">
-        <v>8031700</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
+        <v>8138200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>8028200</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2735,8 +2893,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,28 +3074,31 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1847900</v>
+        <v>-1000300</v>
       </c>
       <c r="E72" s="3">
-        <v>1863600</v>
+        <v>-1056100</v>
       </c>
       <c r="F72" s="3">
-        <v>-833000</v>
+        <v>-1052400</v>
       </c>
       <c r="G72" s="3">
-        <v>-811000</v>
+        <v>-1057500</v>
       </c>
       <c r="H72" s="3">
-        <v>-830400</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+        <v>-651800</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-759200</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2941,8 +3115,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,31 +3238,34 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4104800</v>
+      </c>
+      <c r="E76" s="3">
         <v>4006600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4020500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-160200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-117500</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="J76" s="3">
+        <v>-73900</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3093,8 +3279,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3320,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-94700</v>
-      </c>
       <c r="G81" s="3">
-        <v>-35900</v>
+        <v>-93000</v>
       </c>
       <c r="H81" s="3">
-        <v>-97000</v>
+        <v>-37700</v>
       </c>
       <c r="I81" s="3">
+        <v>-96900</v>
+      </c>
+      <c r="J81" s="3">
         <v>19000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-148300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-73100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-29000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3426,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>62800</v>
+        <v>54100</v>
       </c>
       <c r="E83" s="3">
-        <v>62500</v>
+        <v>52400</v>
       </c>
       <c r="F83" s="3">
-        <v>62400</v>
+        <v>52000</v>
       </c>
       <c r="G83" s="3">
-        <v>54100</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3">
+        <v>46600</v>
+      </c>
+      <c r="H83" s="3">
+        <v>51400</v>
+      </c>
+      <c r="I83" s="3">
+        <v>48200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>48200</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>147700</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3670,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-49700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>116500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>305100</v>
       </c>
-      <c r="G89" s="3">
-        <v>-39200</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="H89" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-124200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>57300</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-179700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,31 +3730,32 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-62600</v>
+        <v>-50900</v>
       </c>
       <c r="E91" s="3">
-        <v>-67300</v>
+        <v>-47400</v>
       </c>
       <c r="F91" s="3">
-        <v>-55700</v>
+        <v>-58700</v>
       </c>
       <c r="G91" s="3">
-        <v>-37400</v>
+        <v>-40700</v>
       </c>
       <c r="H91" s="3">
-        <v>-58700</v>
+        <v>-31900</v>
       </c>
       <c r="I91" s="3">
-        <v>-36400</v>
+        <v>-28900</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-22100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3548,8 +3769,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3851,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-64500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-47100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-67300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-59200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-39300</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="I94" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-82400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,31 +3911,32 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3716,8 +3950,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,118 +4073,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E100" s="3">
         <v>19100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-184900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-62300</v>
       </c>
-      <c r="G100" s="3">
-        <v>92600</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="H100" s="3">
+        <v>67500</v>
+      </c>
+      <c r="I100" s="3">
+        <v>91500</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-86800</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>47800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-3700</v>
+        <v>-8400</v>
       </c>
       <c r="E101" s="3">
-        <v>-10400</v>
+        <v>-8600</v>
       </c>
       <c r="F101" s="3">
-        <v>15500</v>
+        <v>3600</v>
       </c>
       <c r="G101" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
+        <v>37300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-73700</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-81400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-146100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>199100</v>
       </c>
-      <c r="G102" s="3">
-        <v>5700</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="H102" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-69800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>-288000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>AS</t>
   </si>
@@ -656,200 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1635500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1353800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1011100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1182900</v>
       </c>
-      <c r="G8" s="3">
-        <v>1315000</v>
-      </c>
       <c r="H8" s="3">
+        <v>1327500</v>
+      </c>
+      <c r="I8" s="3">
         <v>1153100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>869500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1050300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1198700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>847400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>693500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>809200</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>718000</v>
+      </c>
+      <c r="E9" s="3">
         <v>606500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>442600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>544400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>631800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>564900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>400200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>495400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>596700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>415200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>364700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>408600</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>917500</v>
+      </c>
+      <c r="E10" s="3">
         <v>747300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>568500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>638500</v>
       </c>
-      <c r="G10" s="3">
-        <v>683200</v>
-      </c>
       <c r="H10" s="3">
+        <v>695700</v>
+      </c>
+      <c r="I10" s="3">
         <v>588200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>469300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>554900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>602000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>432200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>328800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>400600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,76 +963,82 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E15" s="3">
         <v>38900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>33600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>36000</v>
       </c>
-      <c r="G15" s="3">
-        <v>33400</v>
-      </c>
       <c r="H15" s="3">
+        <v>34400</v>
+      </c>
+      <c r="I15" s="3">
         <v>32800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>33100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>33200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1029,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1443200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1177100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1018400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1072600</v>
       </c>
-      <c r="G17" s="3">
-        <v>1257900</v>
-      </c>
       <c r="H17" s="3">
+        <v>1270400</v>
+      </c>
+      <c r="I17" s="3">
         <v>1051300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>857300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>917100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1266000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>776600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>706700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>760200</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>192300</v>
+      </c>
+      <c r="E18" s="3">
         <v>176700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>110300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>57100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>101800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>133200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-67300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>70800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>49000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,213 +1174,229 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>14000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3600</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>189300</v>
+      </c>
+      <c r="E21" s="3">
         <v>210800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>21100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>132300</v>
       </c>
-      <c r="G21" s="3">
-        <v>83100</v>
-      </c>
       <c r="H21" s="3">
+        <v>84100</v>
+      </c>
+      <c r="I21" s="3">
         <v>132200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>41800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>163900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>218000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>88900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E22" s="3">
         <v>44100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>68300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>109400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>107000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>97600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>61100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>55000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>54200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>60100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E23" s="3">
         <v>128900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-53700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-55100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-91800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>45600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-124900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-65400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E24" s="3">
         <v>72700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-51900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>39800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>32600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>26600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>23400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11700</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E26" s="3">
         <v>56200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-94900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-97000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-148300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-61600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19200</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E27" s="3">
         <v>55800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-93000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-37700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-96900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-148300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-61600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19200</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1541,19 +1601,22 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-11500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-9800</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-14000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3600</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E33" s="3">
         <v>55800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-93000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-37700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-96900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-148300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-73100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-29000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E35" s="3">
         <v>55800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-93000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-37700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-96900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-148300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-73100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-29000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,32 +1963,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>345400</v>
+      </c>
+      <c r="E41" s="3">
         <v>312000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>255900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>337300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>483400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>284200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>278500</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1919,8 +2005,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1960,32 +2049,35 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>745900</v>
+      </c>
+      <c r="E43" s="3">
         <v>881900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>476600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>567100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>716500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>676900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>469400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2001,32 +2093,35 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1223300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1338500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1241000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1100600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1099600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1197500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1219200</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2042,32 +2137,35 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E45" s="3">
         <v>15900</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>13000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>26200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,32 +2181,35 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2399300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2548300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2192700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2169700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2351700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2360100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2140400</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2124,32 +2225,35 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9000</v>
+        <v>16800</v>
       </c>
       <c r="E47" s="3">
         <v>9000</v>
       </c>
       <c r="F47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G47" s="3">
         <v>9100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8600</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2165,32 +2269,35 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1025300</v>
+      </c>
+      <c r="E48" s="3">
         <v>950400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>806900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>713100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>684100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>605200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>526200</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2206,34 +2313,37 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4665400</v>
+      </c>
+      <c r="E49" s="3">
         <v>5029100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4946800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4966800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5014600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4948200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5007600</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2247,8 +2357,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,32 +2445,35 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>161900</v>
+      </c>
+      <c r="E52" s="3">
         <v>121900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>133700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>155500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>152500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>115100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>120600</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2370,8 +2489,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,32 +2533,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8336300</v>
+      </c>
+      <c r="E54" s="3">
         <v>8828400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8244700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8174500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8373800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8147000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7914200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2452,8 +2577,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,32 +2615,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>549000</v>
+      </c>
+      <c r="E57" s="3">
         <v>482300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>454300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>387400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>426500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>389400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>434200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,34 +2657,37 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>253400</v>
+      </c>
+      <c r="E58" s="3">
         <v>394900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>133300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>99900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>470400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>456300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>335000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2568,32 +2701,35 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>256200</v>
+      </c>
+      <c r="E59" s="3">
         <v>199100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>126600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>193800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>226900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>589300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>442000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,32 +2745,35 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1554400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1571400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1170800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1106200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1573900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1435000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1211200</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2650,32 +2789,35 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1229800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2392500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2343700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2301000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6190800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5982700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6091900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2691,32 +2833,35 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E62" s="3">
         <v>66200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>39800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>67000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>48700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>46000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2732,8 +2877,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,32 +3009,35 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3327900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4716100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4231000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4148800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8530600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8138200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8028200</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2896,8 +3053,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,32 +3247,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-984900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1000300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1056100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1052400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1057500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-651800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-759200</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3118,8 +3291,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,35 +3423,38 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4999300</v>
+      </c>
+      <c r="E76" s="3">
         <v>4104800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4006600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4020500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-160200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-117500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-73900</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3282,8 +3467,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E81" s="3">
         <v>55800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-93000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-37700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-96900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-148300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-73100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-29000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
         <v>54100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>52400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>52000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>51400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>48200</v>
       </c>
       <c r="J83" s="3">
         <v>48200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="K83" s="3">
+        <v>48200</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>147700</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>406800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-48900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-49700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>116500</v>
       </c>
-      <c r="G89" s="3">
-        <v>305100</v>
-      </c>
       <c r="H89" s="3">
+        <v>279900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-14000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-124200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>57300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-179700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,35 +3950,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-72100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-50900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-47400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-31900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -3772,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-47100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-67300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-59200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>-82400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3938,8 +4171,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3953,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,127 +4318,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-251700</v>
+      </c>
+      <c r="E100" s="3">
         <v>151500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>19100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-184900</v>
       </c>
-      <c r="G100" s="3">
-        <v>-62300</v>
-      </c>
       <c r="H100" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="I100" s="3">
         <v>67500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>91500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-86800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>47800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-8400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>37300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-29200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-22300</v>
       </c>
       <c r="J101" s="3">
         <v>-22300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="K101" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>-73700</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E102" s="3">
         <v>56100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-81400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-146100</v>
       </c>
-      <c r="G102" s="3">
-        <v>199100</v>
-      </c>
       <c r="H102" s="3">
+        <v>199000</v>
+      </c>
+      <c r="I102" s="3">
         <v>5800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-69800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-53700</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>-288000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>AS</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1472500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1635500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1353800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1011100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1182900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1327500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1153100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>869500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1050300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1198700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>847400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>693500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>809200</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>621400</v>
+      </c>
+      <c r="E9" s="3">
         <v>718000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>606500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>442600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>544400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>631800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>564900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>400200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>495400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>596700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>415200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>364700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>408600</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>851100</v>
+      </c>
+      <c r="E10" s="3">
         <v>917500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>747300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>568500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>638500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>695700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>588200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>469300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>554900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>602000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>432200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>328800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>400600</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +891,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,82 +983,88 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>16200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>1200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E15" s="3">
         <v>40600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>33600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>36000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>34400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>33100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>33200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1258000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1443200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1177100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1018400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1072600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1270400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1051300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>857300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>917100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1266000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>776600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>706700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>760200</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E18" s="3">
         <v>192300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>176700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>110300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>57100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>101800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>133200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-67300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>70800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,228 +1208,244 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>43600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3600</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>255700</v>
+      </c>
+      <c r="E21" s="3">
         <v>189300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>210800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>21100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>132300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>84100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>132200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>41800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>163900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>218000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>88900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E22" s="3">
         <v>64100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>44100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>42500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>68300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>109400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>107000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>97600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>83600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>61100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>55000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>54200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>60100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>197600</v>
+      </c>
+      <c r="E23" s="3">
         <v>70900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>128900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-53700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-55100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-91800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-124900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-65400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7500</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E24" s="3">
         <v>53800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>72700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-51900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>39800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>32600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>23400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11700</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>138100</v>
+      </c>
+      <c r="E26" s="3">
         <v>17100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>56200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-94900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-35900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-97000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-148300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-61600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19200</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E27" s="3">
         <v>15400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>55800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-93000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-37700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-96900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-148300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-61600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19200</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1604,19 +1665,22 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-11500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-9800</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-43600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3600</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E33" s="3">
         <v>15400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>55800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-93000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-37700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-96900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-148300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-73100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-29000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E35" s="3">
         <v>15400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>55800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-93000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-37700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-96900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-148300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-73100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-29000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,35 +2050,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>422100</v>
+      </c>
+      <c r="E41" s="3">
         <v>345400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>312000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>255900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>337300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>483400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>284200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>278500</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2008,8 +2095,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,35 +2142,38 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>561400</v>
+      </c>
+      <c r="E43" s="3">
         <v>745900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>881900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>476600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>567100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>716500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>676900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>469400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,35 +2189,38 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1267200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1223300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1338500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1241000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1100600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1099600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1197500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1219200</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2140,35 +2236,38 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>45300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15900</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>13000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>26200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,35 +2283,38 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2444400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2399300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2548300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2192700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2169700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2351700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2360100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2140400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,35 +2330,38 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E47" s="3">
         <v>16800</v>
-      </c>
-      <c r="E47" s="3">
-        <v>9000</v>
       </c>
       <c r="F47" s="3">
         <v>9000</v>
       </c>
       <c r="G47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="H47" s="3">
         <v>9100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2272,35 +2377,38 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1126600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1025300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>950400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>806900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>713100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>684100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>605200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>526200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2316,37 +2424,40 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4800300</v>
+      </c>
+      <c r="E49" s="3">
         <v>4665400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5029100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4946800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4966800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5014600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4948200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5007600</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,35 +2565,38 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E52" s="3">
         <v>161900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>121900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>133700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>155500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>152500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>115100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>120600</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,35 +2659,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8527400</v>
+      </c>
+      <c r="E54" s="3">
         <v>8336300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8828400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8244700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8174500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8373800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8147000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7914200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2580,8 +2706,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,35 +2746,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>457000</v>
+      </c>
+      <c r="E57" s="3">
         <v>549000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>482300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>454300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>387400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>426500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>389400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>434200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2660,37 +2791,40 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E58" s="3">
         <v>253400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>394900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>133300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>99900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>470400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>456300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>335000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2704,35 +2838,38 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>752700</v>
+      </c>
+      <c r="E59" s="3">
         <v>256200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>199100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>126600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>193800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>226900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>589300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>442000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,35 +2885,38 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1468700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1554400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1571400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1170800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1106200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1573900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1435000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1211200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,35 +2932,38 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1275300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1229800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2392500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2343700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2301000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6190800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5982700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6091900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2836,35 +2979,38 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E62" s="3">
         <v>26300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>66200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>67000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>48700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,35 +3167,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3296600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3327900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4716100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4231000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4148800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8530600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8138200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8028200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3214,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,35 +3421,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-780300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-984900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1000300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1056100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1052400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1057500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-651800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-759200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3294,8 +3468,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,38 +3609,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5218200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4999300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4104800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4006600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4020500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-160200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-117500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-73900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3656,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E81" s="3">
         <v>15400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>55800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-93000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-37700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-96900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-148300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-73100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-29000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +3823,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>54100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>52400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>52000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>51400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>48200</v>
       </c>
       <c r="K83" s="3">
         <v>48200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="L83" s="3">
+        <v>48200</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>147700</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>406800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-48900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-49700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>116500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>279900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-124200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>57300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-179700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,38 +4171,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-72100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-50900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-47400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-40700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-31900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -3995,8 +4216,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>-89400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-64500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-47100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-67300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-59200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-39300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-82400</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4174,8 +4408,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,136 +4564,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>-251700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>151500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-184900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-37200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>67500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>91500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-86800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>47800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E101" s="3">
         <v>15500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>37300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-29200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-22300</v>
       </c>
       <c r="K101" s="3">
         <v>-22300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="L101" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-73700</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>33400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>56100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-81400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-146100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>199000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-69800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-53700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>-288000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
   <si>
     <t>AS</t>
   </si>
@@ -656,225 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1236300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1472500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1635500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1353800</v>
       </c>
-      <c r="G8" s="3">
-        <v>1011100</v>
-      </c>
       <c r="H8" s="3">
-        <v>1182900</v>
+        <v>1001400</v>
       </c>
       <c r="I8" s="3">
+        <v>1192500</v>
+      </c>
+      <c r="J8" s="3">
         <v>1327500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1153100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>869500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1050300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1198700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>847400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>693500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>809200</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>513400</v>
+      </c>
+      <c r="E9" s="3">
         <v>621400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>718000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>606500</v>
       </c>
-      <c r="G9" s="3">
-        <v>442600</v>
-      </c>
       <c r="H9" s="3">
+        <v>442500</v>
+      </c>
+      <c r="I9" s="3">
         <v>544400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>631800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>564900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>400200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>495400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>596700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>415200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>364700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>408600</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>722900</v>
+      </c>
+      <c r="E10" s="3">
         <v>851100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>917500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>747300</v>
       </c>
-      <c r="G10" s="3">
-        <v>568500</v>
-      </c>
       <c r="H10" s="3">
-        <v>638500</v>
+        <v>558900</v>
       </c>
       <c r="I10" s="3">
+        <v>648100</v>
+      </c>
+      <c r="J10" s="3">
         <v>695700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>588200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>469300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>554900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>602000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>432200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>328800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>400600</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,88 +1003,94 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>16200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>1200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>37300</v>
+        <v>42100</v>
       </c>
       <c r="E15" s="3">
+        <v>41800</v>
+      </c>
+      <c r="F15" s="3">
         <v>40600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>38900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>33600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>36000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>34400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>33100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>33200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1258000</v>
+        <v>1190100</v>
       </c>
       <c r="E17" s="3">
+        <v>1258100</v>
+      </c>
+      <c r="F17" s="3">
         <v>1443200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1177100</v>
       </c>
-      <c r="G17" s="3">
-        <v>1018400</v>
-      </c>
       <c r="H17" s="3">
-        <v>1072600</v>
+        <v>1009000</v>
       </c>
       <c r="I17" s="3">
+        <v>1082300</v>
+      </c>
+      <c r="J17" s="3">
         <v>1270400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1051300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>857300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>917100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1266000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>776600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>706700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>760200</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>214500</v>
+        <v>46200</v>
       </c>
       <c r="E18" s="3">
+        <v>214400</v>
+      </c>
+      <c r="F18" s="3">
         <v>192300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>176700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-7300</v>
-      </c>
       <c r="H18" s="3">
-        <v>110300</v>
+        <v>-7600</v>
       </c>
       <c r="I18" s="3">
+        <v>110200</v>
+      </c>
+      <c r="J18" s="3">
         <v>57100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>101800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>133200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-67300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>70800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>49000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,243 +1242,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>43600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4800</v>
       </c>
-      <c r="G20" s="3">
-        <v>5200</v>
-      </c>
       <c r="H20" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I20" s="3">
         <v>14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>255700</v>
+        <v>95000</v>
       </c>
       <c r="E21" s="3">
+        <v>260100</v>
+      </c>
+      <c r="F21" s="3">
         <v>189300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>210800</v>
       </c>
-      <c r="G21" s="3">
-        <v>21100</v>
-      </c>
       <c r="H21" s="3">
-        <v>132300</v>
+        <v>20900</v>
       </c>
       <c r="I21" s="3">
+        <v>132200</v>
+      </c>
+      <c r="J21" s="3">
         <v>84100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>132200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>41800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>163900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>218000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>88900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>22000</v>
+        <v>29900</v>
       </c>
       <c r="E22" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F22" s="3">
         <v>64100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>44100</v>
       </c>
-      <c r="G22" s="3">
-        <v>42500</v>
-      </c>
       <c r="H22" s="3">
-        <v>68300</v>
+        <v>42300</v>
       </c>
       <c r="I22" s="3">
+        <v>68200</v>
+      </c>
+      <c r="J22" s="3">
         <v>109400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>107000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>97600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>83600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>61100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>55000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>54200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>60100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E23" s="3">
         <v>197600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>70900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>128900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-53700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-55100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-91800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-124900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-65400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E24" s="3">
         <v>59500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>53800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>72700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-51900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>32600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>17000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11700</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E26" s="3">
         <v>138100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>56200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-94900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-35900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-97000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-148300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-61600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E27" s="3">
         <v>134600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>55800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-93000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-37700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-96900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-148300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-61600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1668,19 +1729,22 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-11500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E32" s="3">
         <v>3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-43600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E33" s="3">
         <v>134600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>55800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-93000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-37700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-96900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-148300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-73100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E35" s="3">
         <v>134600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>55800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-93000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-37700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-96900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-148300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-73100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,38 +2137,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>303400</v>
+      </c>
+      <c r="E41" s="3">
         <v>422100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>345400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>312000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>255900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>337300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>483400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>284200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>278500</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2098,8 +2185,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,38 +2235,41 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>561400</v>
+        <v>651300</v>
       </c>
       <c r="E43" s="3">
+        <v>729700</v>
+      </c>
+      <c r="F43" s="3">
         <v>745900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>881900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>476600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>567100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>716500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>676900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>469400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,38 +2285,41 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1597000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1267200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1223300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1338500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1241000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1100600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1099600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1197500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1219200</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2239,38 +2335,41 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>24900</v>
       </c>
       <c r="E45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="F45" s="3">
         <v>45300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15900</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>26200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,38 +2385,41 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2576600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2444400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2399300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2548300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2192700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2169700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2351700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2360100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2140400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,38 +2435,41 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E47" s="3">
         <v>16900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16800</v>
-      </c>
-      <c r="F47" s="3">
-        <v>9000</v>
       </c>
       <c r="G47" s="3">
         <v>9000</v>
       </c>
       <c r="H47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I47" s="3">
         <v>9100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2380,38 +2485,41 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1126600</v>
+        <v>1139700</v>
       </c>
       <c r="E48" s="3">
+        <v>1069800</v>
+      </c>
+      <c r="F48" s="3">
         <v>1025300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>950400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>806900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>713100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>684100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>605200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>526200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2427,40 +2535,43 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5066000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4800300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4665400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5029100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4946800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4966800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5014600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4948200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5007600</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,38 +2685,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>57500</v>
+        <v>91700</v>
       </c>
       <c r="E52" s="3">
+        <v>114300</v>
+      </c>
+      <c r="F52" s="3">
         <v>161900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>121900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>133700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>155500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>152500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>115100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>120600</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,38 +2785,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9018900</v>
+      </c>
+      <c r="E54" s="3">
         <v>8527400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8336300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8828400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8244700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8174500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8373800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8147000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7914200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2709,8 +2835,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,38 +2877,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>529200</v>
+      </c>
+      <c r="E57" s="3">
         <v>457000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>549000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>482300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>454300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>387400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>426500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>389400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>434200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,40 +2925,43 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>277100</v>
+      </c>
+      <c r="E58" s="3">
         <v>259000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>253400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>394900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>133300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>99900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>470400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>456300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>335000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2841,38 +2975,41 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>752700</v>
+        <v>327700</v>
       </c>
       <c r="E59" s="3">
+        <v>286800</v>
+      </c>
+      <c r="F59" s="3">
         <v>256200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>199100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>126600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>193800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>226900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>589300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>442000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,38 +3025,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1612000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1468700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1554400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1571400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1170800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1106200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1573900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1435000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1211200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,38 +3075,41 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1307900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1275300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1229800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2392500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2343700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2301000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6190800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5982700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6091900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2982,38 +3125,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E62" s="3">
         <v>25500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>67000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>48700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>46000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,38 +3325,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3495100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3296600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3327900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4716100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4231000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4148800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8530600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8138200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8028200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3375,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,38 +3595,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-780300</v>
+        <v>-832100</v>
       </c>
       <c r="E72" s="3">
+        <v>-850300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-984900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1000300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1056100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1052400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1057500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-651800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-759200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3645,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,41 +3795,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5507000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5218200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4999300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4104800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4006600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4020500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-160200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-117500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-73900</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,8 +3845,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E81" s="3">
         <v>134600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>55800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-93000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-37700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-96900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-148300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-73100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4022,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E83" s="3">
         <v>62500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>54100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>52400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>52000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>51400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>48200</v>
       </c>
       <c r="L83" s="3">
         <v>48200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="M83" s="3">
+        <v>48200</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>147700</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-56200</v>
       </c>
       <c r="E89" s="3">
+        <v>163700</v>
+      </c>
+      <c r="F89" s="3">
         <v>406800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-48900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-49700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>116500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>279900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-124200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>57300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-179700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,41 +4392,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-44600</v>
       </c>
       <c r="E91" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-72100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-50900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-47400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-31900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -4219,8 +4440,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-66000</v>
       </c>
       <c r="E94" s="3">
+        <v>-69200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-89400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-64500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-47100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-67300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-59200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-82400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4411,8 +4645,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,145 +4810,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>-10900</v>
       </c>
       <c r="E100" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-251700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>151500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>19100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-184900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-37200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>67500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>91500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-86800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>47800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>37300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-29200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-22300</v>
       </c>
       <c r="L101" s="3">
         <v>-22300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="M101" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-73700</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-118700</v>
       </c>
       <c r="E102" s="3">
+        <v>76700</v>
+      </c>
+      <c r="F102" s="3">
         <v>33400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>56100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-81400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-146100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>199000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-69800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-53700</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>-288000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>AS</t>
   </si>
@@ -656,251 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2101100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1756300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1236300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1472500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1635500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1353800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1001400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1192500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1327500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1153100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>869500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1050300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1198700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>847400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>693500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>809200</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>889000</v>
+      </c>
+      <c r="E9" s="3">
         <v>758100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>513400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>621400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>718000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>606500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>442500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>544400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>631800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>564900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>400200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>495400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>596700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>415200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>364700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>408600</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1212100</v>
+      </c>
+      <c r="E10" s="3">
         <v>998200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>722900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>851100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>917500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>747300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>558900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>648100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>695700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>588200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>469300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>554900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>602000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>432200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>328800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>400600</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,100 +1042,106 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E14" s="3">
         <v>10200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>16200</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>15600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2800</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E15" s="3">
         <v>76000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>42100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>41800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>40600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>38900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>33600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>33100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>33200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1132,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1873300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1530300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1190100</v>
       </c>
-      <c r="F17" s="3">
-        <v>1258100</v>
-      </c>
       <c r="G17" s="3">
-        <v>1443200</v>
+        <v>1258000</v>
       </c>
       <c r="H17" s="3">
+        <v>1444900</v>
+      </c>
+      <c r="I17" s="3">
         <v>1177100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1009000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1082300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1270400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1051300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>857300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>917100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1266000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>776600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>706700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>760200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>227800</v>
+      </c>
+      <c r="E18" s="3">
         <v>226000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46200</v>
       </c>
-      <c r="F18" s="3">
-        <v>214400</v>
-      </c>
       <c r="G18" s="3">
-        <v>192300</v>
+        <v>214500</v>
       </c>
       <c r="H18" s="3">
+        <v>190600</v>
+      </c>
+      <c r="I18" s="3">
         <v>176700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>110200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>57100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>101800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>133200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-67300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>70800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>49000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,273 +1309,289 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>43600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>281200</v>
+      </c>
+      <c r="E21" s="3">
         <v>307900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>95000</v>
       </c>
-      <c r="F21" s="3">
-        <v>260100</v>
-      </c>
       <c r="G21" s="3">
-        <v>189300</v>
+        <v>260200</v>
       </c>
       <c r="H21" s="3">
+        <v>187600</v>
+      </c>
+      <c r="I21" s="3">
         <v>210800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>20900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>132200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>84100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>132200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>41800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>163900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>218000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>88900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E22" s="3">
         <v>25500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>29900</v>
       </c>
-      <c r="F22" s="3">
-        <v>21900</v>
-      </c>
       <c r="G22" s="3">
-        <v>64100</v>
+        <v>22000</v>
       </c>
       <c r="H22" s="3">
+        <v>64500</v>
+      </c>
+      <c r="I22" s="3">
         <v>44100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>42300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>68200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>109400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>107000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>97600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>83600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>61100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>55000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>54200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>60100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>207400</v>
+      </c>
+      <c r="E23" s="3">
         <v>197700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>197600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>70900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>128900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-53700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-55100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-91800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-124900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-65400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7500</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E24" s="3">
         <v>51300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>59500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>53800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>72700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-51900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>39800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>32600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>26600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>17000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11700</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E26" s="3">
         <v>146400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>138100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>56200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-94900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-35900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-97000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-148300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-61600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-19200</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E27" s="3">
         <v>143100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>134600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>55800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-93000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-37700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-96900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-148300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-61600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-19200</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1796,19 +1856,22 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-11500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-9800</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>5900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-43600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E33" s="3">
         <v>143100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>134600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>55800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-93000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-37700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-96900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-148300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-73100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-29000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E35" s="3">
         <v>143100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>134600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>55800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-93000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-37700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-96900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-148300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-73100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-29000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,44 +2310,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>652300</v>
+      </c>
+      <c r="E41" s="3">
         <v>353300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>303400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>422100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>345400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>312000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>255900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>337300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>483400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>284200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>278500</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,8 +2364,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2331,44 +2420,47 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>952300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1084600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>651300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>729700</v>
       </c>
-      <c r="G43" s="3">
-        <v>745900</v>
-      </c>
       <c r="H43" s="3">
+        <v>806500</v>
+      </c>
+      <c r="I43" s="3">
         <v>881900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>476600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>567100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>716500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>676900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>469400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2384,44 +2476,47 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1622100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1710400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1597000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1267200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1223300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1338500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1241000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1100600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1099600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1197500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1219200</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2437,44 +2532,47 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E45" s="3">
         <v>23000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25400</v>
       </c>
-      <c r="G45" s="3">
-        <v>45300</v>
-      </c>
       <c r="H45" s="3">
+        <v>44500</v>
+      </c>
+      <c r="I45" s="3">
         <v>15900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>13000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>26200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,44 +2588,47 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3171300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2576600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2444400</v>
       </c>
-      <c r="G46" s="3">
-        <v>2399300</v>
-      </c>
       <c r="H46" s="3">
+        <v>2459100</v>
+      </c>
+      <c r="I46" s="3">
         <v>2548300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2192700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2169700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2351700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2360100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2140400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,44 +2644,47 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E47" s="3">
         <v>67200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>60600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16900</v>
       </c>
-      <c r="G47" s="3">
-        <v>16800</v>
-      </c>
       <c r="H47" s="3">
-        <v>9000</v>
+        <v>12600</v>
       </c>
       <c r="I47" s="3">
         <v>9000</v>
       </c>
       <c r="J47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K47" s="3">
         <v>9100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2596,44 +2700,47 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1404100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1245200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1139700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1069800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1025300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>950400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>806900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>713100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>684100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>605200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>526200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,46 +2756,49 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5042900</v>
+      </c>
+      <c r="E49" s="3">
         <v>5068600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5066000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4800300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4665400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5029100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4946800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4966800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5014600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4948200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5007600</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -2702,8 +2812,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,44 +2924,47 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E52" s="3">
         <v>77800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>91700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>114300</v>
       </c>
-      <c r="G52" s="3">
-        <v>161900</v>
-      </c>
       <c r="H52" s="3">
+        <v>166100</v>
+      </c>
+      <c r="I52" s="3">
         <v>121900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>133700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>155500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>152500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>115100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>120600</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2861,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,44 +3036,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10064400</v>
+      </c>
+      <c r="E54" s="3">
         <v>9711500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9018900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8527400</v>
       </c>
-      <c r="G54" s="3">
-        <v>8336300</v>
-      </c>
       <c r="H54" s="3">
+        <v>8396100</v>
+      </c>
+      <c r="I54" s="3">
         <v>8828400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8244700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8174500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8373800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8147000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7914200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2967,8 +3092,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,44 +3138,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>769800</v>
+      </c>
+      <c r="E57" s="3">
         <v>564500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>529200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>457000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>549000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>482300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>454300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>387400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>426500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>389400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>434200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3062,46 +3192,49 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>299900</v>
+      </c>
+      <c r="E58" s="3">
         <v>501100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>277100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>259000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>253400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>394900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>133300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>99900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>470400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>456300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>335000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -3115,44 +3248,47 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>473400</v>
+        <v>494000</v>
       </c>
       <c r="E59" s="3">
-        <v>327700</v>
+        <v>373200</v>
       </c>
       <c r="F59" s="3">
+        <v>238400</v>
+      </c>
+      <c r="G59" s="3">
         <v>286800</v>
       </c>
-      <c r="G59" s="3">
-        <v>256200</v>
-      </c>
       <c r="H59" s="3">
+        <v>270500</v>
+      </c>
+      <c r="I59" s="3">
         <v>199100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>126600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>193800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>226900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>589300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>442000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,44 +3304,47 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2209200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2098500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1612000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1468700</v>
       </c>
-      <c r="G60" s="3">
-        <v>1554400</v>
-      </c>
       <c r="H60" s="3">
+        <v>1614200</v>
+      </c>
+      <c r="I60" s="3">
         <v>1571400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1170800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1106200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1573900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1435000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1211200</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,44 +3360,47 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1453200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1366800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1307900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1275300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1229800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2392500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2343700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2301000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6190800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5982700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6091900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3274,44 +3416,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E62" s="3">
         <v>26700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>66200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>57700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>67000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>46000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,44 +3640,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4243500</v>
+      </c>
+      <c r="E66" s="3">
         <v>4044700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3495100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3296600</v>
       </c>
-      <c r="G66" s="3">
-        <v>3327900</v>
-      </c>
       <c r="H66" s="3">
+        <v>3387700</v>
+      </c>
+      <c r="I66" s="3">
         <v>4716100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4231000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4148800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8530600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8138200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8028200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3539,8 +3696,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,44 +3942,47 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-557500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-689000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-832100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-850300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-984900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1000300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1056100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1052400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1057500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-651800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-759200</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3825,8 +3998,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,47 +4166,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5802000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5646700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5507000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5218200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4999300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4104800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4006600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4020500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-160200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-117500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-73900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4037,8 +4222,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E81" s="3">
         <v>143100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>134600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>55800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-93000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-37700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-96900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-148300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-73100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-29000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E83" s="3">
         <v>71200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>62800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>62500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>54100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>52400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>52000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>51400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>48200</v>
       </c>
       <c r="N83" s="3">
         <v>48200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="O83" s="3">
+        <v>48200</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>147700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>625400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-56200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>163700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>406800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-48900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-49700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>116500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>279900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-124200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>57300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-179700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,47 +4833,48 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-56100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-44600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-41100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-72100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-50900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-47400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-31900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -4667,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-94800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-108100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-66000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-69200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-89400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-64500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-47100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-67300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-59200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4885,8 +5118,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4900,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,163 +5301,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-238300</v>
+      </c>
+      <c r="E100" s="3">
         <v>152600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-251700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>151500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>19100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-184900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>67500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>91500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-86800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>47800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E101" s="3">
         <v>18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-10400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>15500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>37300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-29200</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-22300</v>
       </c>
       <c r="N101" s="3">
         <v>-22300</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="O101" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-73700</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E102" s="3">
         <v>49900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-118700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>76700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>33400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>56100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-81400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-146100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>199000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-69800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-53700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-288000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>AS</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1945500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2101100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1756300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1236300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1472500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1635500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1353800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1001400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1192500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1327500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1153100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>869500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1050300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1198700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>847400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>693500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>809200</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>780100</v>
+      </c>
+      <c r="E9" s="3">
         <v>889000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>758100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>513400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>621400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>718000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>606500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>442500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>544400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>631800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>564900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>495400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>596700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>415200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>364700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>408600</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1165400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1212100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>998200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>722900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>851100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>917500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>747300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>558900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>648100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>695700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>588200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>469300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>554900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>602000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>432200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>328800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>400600</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,106 +1062,112 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>15600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2800</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E15" s="3">
         <v>55900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>76000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>42100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>41800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>40600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>38900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>33600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>34400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>33100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>33200</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1873300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1530300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1190100</v>
       </c>
-      <c r="G17" s="3">
-        <v>1258000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1258100</v>
+      </c>
+      <c r="I17" s="3">
         <v>1444900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1177100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1009000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1082300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1270400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1051300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>857300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>917100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1266000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>776600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>706700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>760200</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>321500</v>
+      </c>
+      <c r="E18" s="3">
         <v>227800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>226000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46200</v>
       </c>
-      <c r="G18" s="3">
-        <v>214500</v>
-      </c>
       <c r="H18" s="3">
+        <v>214400</v>
+      </c>
+      <c r="I18" s="3">
         <v>190600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>176700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>110200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>57100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>101800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>133200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-67300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>70800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>49000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,288 +1343,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>43600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>366700</v>
+      </c>
+      <c r="E21" s="3">
         <v>281200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>307900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>95000</v>
       </c>
-      <c r="G21" s="3">
-        <v>260200</v>
-      </c>
       <c r="H21" s="3">
+        <v>260100</v>
+      </c>
+      <c r="I21" s="3">
         <v>187600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>210800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>20900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>132200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>84100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>132200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>41800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>163900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>218000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>88900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E22" s="3">
         <v>20400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29900</v>
       </c>
-      <c r="G22" s="3">
-        <v>22000</v>
-      </c>
       <c r="H22" s="3">
+        <v>21900</v>
+      </c>
+      <c r="I22" s="3">
         <v>64500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>44100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>42300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>68200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>109400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>107000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>97600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>83600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>61100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>55000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>54200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>60100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>240600</v>
+      </c>
+      <c r="E23" s="3">
         <v>207400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>197700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>197600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>70900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>128900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-53700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-55100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-91800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-124900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>15300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-65400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E24" s="3">
         <v>73900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>51300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>53800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>72700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-51900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>32600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>17000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11700</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>170100</v>
+      </c>
+      <c r="E26" s="3">
         <v>133500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>146400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>138100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>56200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-94900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-35900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-97000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-148300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-61600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-19200</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E27" s="3">
         <v>131500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>143100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>134600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>55800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-93000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-96900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-148300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-61600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-19200</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1859,19 +1920,22 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-11500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-9800</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-43600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E33" s="3">
         <v>131500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>143100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>134600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>55800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-93000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-37700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-96900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-148300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-73100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-29000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E35" s="3">
         <v>131500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>143100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>134600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>55800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-93000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-37700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-96900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-148300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-73100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-29000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,47 +2397,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>683700</v>
+      </c>
+      <c r="E41" s="3">
         <v>652300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>353300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>303400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>422100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>345400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>312000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>255900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>337300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>483400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>284200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>278500</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2454,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,47 +2513,50 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>923200</v>
+      </c>
+      <c r="E43" s="3">
         <v>952300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1084600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>651300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>729700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>806500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>881900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>476600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>567100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>716500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>676900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>469400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2479,47 +2572,50 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1687900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1622100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1710400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1597000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1267200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1223300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1338500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1241000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1100600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1099600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1197500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1219200</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,47 +2631,50 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E45" s="3">
         <v>22300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>44500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>13000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3">
         <v>26200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,47 +2690,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3318300</v>
+      </c>
+      <c r="E46" s="3">
         <v>3304000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3171300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2576600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2444400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2459100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2548300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2192700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2169700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2351700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2360100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2140400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,47 +2749,50 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E47" s="3">
         <v>14300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>67200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>60600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12600</v>
-      </c>
-      <c r="I47" s="3">
-        <v>9000</v>
       </c>
       <c r="J47" s="3">
         <v>9000</v>
       </c>
       <c r="K47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L47" s="3">
         <v>9100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8600</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2703,47 +2808,50 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1428500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1404100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1245200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1139700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1069800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1025300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>950400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>806900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>713100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>684100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>605200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>526200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2759,49 +2867,52 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5031900</v>
+      </c>
+      <c r="E49" s="3">
         <v>5042900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5068600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5066000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4800300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4665400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5029100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4946800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4966800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5014600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4948200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5007600</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,47 +3044,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E52" s="3">
         <v>215000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>77800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>91700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>114300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>166100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>121900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>133700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>155500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>152500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>115100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>120600</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,47 +3162,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10010600</v>
+      </c>
+      <c r="E54" s="3">
         <v>10064400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9711500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9018900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8527400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8396100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8828400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8244700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8174500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8373800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8147000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7914200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,47 +3269,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>672600</v>
+      </c>
+      <c r="E57" s="3">
         <v>769800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>564500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>529200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>457000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>549000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>482300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>454300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>387400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>426500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>389400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>434200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3195,49 +3326,52 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>309900</v>
+      </c>
+      <c r="E58" s="3">
         <v>299900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>501100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>277100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>259000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>253400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>394900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>133300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>99900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>470400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>456300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>335000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3251,47 +3385,50 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>475100</v>
+      </c>
+      <c r="E59" s="3">
         <v>494000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>373200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>238400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>286800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>270500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>199100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>126600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>193800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>226900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>589300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>442000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,47 +3444,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1994000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2209200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2098500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1612000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1468700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1614200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1571400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1170800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1106200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1573900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1435000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1211200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,47 +3503,50 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>691100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1453200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1366800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1307900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1275300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1229800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2392500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2343700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2301000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6190800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5982700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6091900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3419,47 +3562,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E62" s="3">
         <v>27700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>66200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>57700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>67000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>48700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>46000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,47 +3798,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3255000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4243500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4044700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3495100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3296600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3387700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4716100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4231000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4148800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8530600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8138200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8028200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3699,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,47 +4116,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-392900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-557500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-689000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-832100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-850300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-984900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1000300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1056100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1052400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1057500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-651800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-759200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,50 +4352,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6744200</v>
+      </c>
+      <c r="E76" s="3">
         <v>5802000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5646700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5507000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5218200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4999300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4104800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4006600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4020500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-160200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-117500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-73900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4225,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E81" s="3">
         <v>131500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>143100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>134600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>55800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-93000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-37700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-96900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-148300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-73100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-29000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E83" s="3">
         <v>15800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>71200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>62800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>62500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>54100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>52400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>52000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>51400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>48200</v>
       </c>
       <c r="O83" s="3">
         <v>48200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="P83" s="3">
+        <v>48200</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>147700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>171500</v>
+      </c>
+      <c r="E89" s="3">
         <v>625400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-56200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>163700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>406800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-48900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-49700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>116500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>279900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-124200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>57300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-179700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,50 +5054,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-74100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-74700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-56100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-44600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-72100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-50900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-40700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-31900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-94800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-108100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-66000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-69200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-89400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-47100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-67300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-59200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-82400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5121,8 +5355,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-47300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-238300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>152600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-27400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-251700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>151500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>19100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-184900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-37200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>67500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>91500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-86800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>47800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-32300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-10400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>15500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>37300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-29200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-22300</v>
       </c>
       <c r="O101" s="3">
         <v>-22300</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="P101" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>-73700</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E102" s="3">
         <v>299000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>49900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-118700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>76700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>33400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>56100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-81400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-146100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>199000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-69800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-53700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-288000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
